--- a/outputs_xlsx_solution/test_new3.4-wide-NF-1.xlsx
+++ b/outputs_xlsx_solution/test_new3.4-wide-NF-1.xlsx
@@ -156,6 +156,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -2062,10 +2068,26 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>39</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
